--- a/results/[15_expiring_support_res]_#_inv_cost.xlsx
+++ b/results/[15_expiring_support_res]_#_inv_cost.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2030" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2035" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2040" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2045" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2050" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2035" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2040" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2045" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2050" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,13 +512,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>27344.79376401644</v>
+        <v>78267.5228613598</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>43118.14902211931</v>
       </c>
       <c r="C2" t="n">
-        <v>338476.3392123409</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -527,13 +527,13 @@
         <v>2028068.080011294</v>
       </c>
       <c r="F2" t="n">
-        <v>66031.94130051559</v>
+        <v>132543.1003192607</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>17739.94550154473</v>
+        <v>18032.32371121224</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -551,10 +551,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>16546.64288761081</v>
+        <v>20953.34586361744</v>
       </c>
       <c r="O2" t="n">
-        <v>13958.09472280542</v>
+        <v>13730.00493738164</v>
       </c>
     </row>
   </sheetData>
@@ -650,13 +650,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>21592.57045775699</v>
+        <v>493494.6883094098</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1046919.912227992</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>49135.65987497274</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>39621.69926764297</v>
+        <v>39343.93996845884</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>36154.41480859539</v>
+        <v>69853.52397059879</v>
       </c>
       <c r="O2" t="n">
-        <v>29802.34554031803</v>
+        <v>30019.03083647061</v>
       </c>
     </row>
   </sheetData>
@@ -788,13 +788,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>242452.4252219552</v>
+        <v>486994.7253484501</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>943335.270081223</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -803,13 +803,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1425.925979620855</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>39373.98526588717</v>
+        <v>39337.7908883909</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>26524.46660634092</v>
       </c>
       <c r="N2" t="n">
-        <v>53308.16490721726</v>
+        <v>108849.6084101741</v>
       </c>
       <c r="O2" t="n">
-        <v>30023.09380555204</v>
+        <v>30052.3473966838</v>
       </c>
     </row>
   </sheetData>
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>11578.49752443177</v>
+        <v>13108.7721587798</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76705.58894163162</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1930.947398408091</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1103,10 +1103,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>28147.3462746636</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>8312.661449003012</v>
+        <v>8317.416250711376</v>
       </c>
     </row>
   </sheetData>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>825221.7306868637</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>

--- a/results/[15_expiring_support_res]_#_inv_cost.xlsx
+++ b/results/[15_expiring_support_res]_#_inv_cost.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2030" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2035" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2040" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2045" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2050" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2035" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2040" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2045" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2050" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,13 +512,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22766.094180751</v>
+        <v>78267.5228613598</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>43118.14902211931</v>
       </c>
       <c r="C2" t="n">
-        <v>378680.1067536479</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -527,13 +527,13 @@
         <v>2028068.080011294</v>
       </c>
       <c r="F2" t="n">
-        <v>57851.28911090882</v>
+        <v>132543.1003192607</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>19405.9546141152</v>
+        <v>18032.32371121224</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -551,10 +551,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>12747.72254752198</v>
+        <v>20953.34586361744</v>
       </c>
       <c r="O2" t="n">
-        <v>12641.78914127248</v>
+        <v>13730.00493738164</v>
       </c>
     </row>
   </sheetData>
@@ -650,13 +650,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112629.9862294005</v>
+        <v>493494.6883094098</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1846412.840537021</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>76400.33709596355</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>63926.54988066799</v>
+        <v>39343.93996845884</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>94095.9368774546</v>
+        <v>69853.52397059879</v>
       </c>
       <c r="O2" t="n">
-        <v>55904.75915466233</v>
+        <v>30019.03083647061</v>
       </c>
     </row>
   </sheetData>
@@ -788,7 +788,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>486994.7253484501</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -809,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>39337.7908883909</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>26524.46660634092</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>108849.6084101741</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>30052.3473966838</v>
       </c>
     </row>
   </sheetData>
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>13108.7721587798</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1106,7 +1106,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>8317.416250711376</v>
       </c>
     </row>
   </sheetData>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>825221.7306868637</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
